--- a/data/CPS/employment_level_native.xlsx
+++ b/data/CPS/employment_level_native.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="378" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="381" uniqueCount="15">
   <si>
     <t>year</t>
   </si>
@@ -103,7 +103,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C376"/>
+  <dimension ref="A1:C379"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4242,6 +4242,39 @@
         <v>129410647.38859878</v>
       </c>
     </row>
+    <row r="377">
+      <c r="A377" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B377" t="s">
+        <v>5</v>
+      </c>
+      <c r="C377" s="1">
+        <v>130551218.69539981</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B378" t="s">
+        <v>6</v>
+      </c>
+      <c r="C378" s="1">
+        <v>129817518.73050074</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B379" t="s">
+        <v>7</v>
+      </c>
+      <c r="C379" s="1">
+        <v>131091811.5057998</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>